--- a/docs/triton-learning/cards/triton-lesson-08-grouped-gemm-correction.xlsx
+++ b/docs/triton-learning/cards/triton-lesson-08-grouped-gemm-correction.xlsx
@@ -41,12 +41,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">一块 GPU 有 60 个 SM。逐个调用矩阵乘 kernel 时，某个小问题只有 8 块，所以这次只发射 8 个 CTA。应该怎样描述这次调用对硬件的利用程度？</t>
+          <t xml:space="preserve">一块 GPU 有 60 个 SM。逐个调用矩阵乘 kernel 时，某个小问题只有 8 块，所以这次只发射 8 个 CTA。应该怎样描述这次调用的利用率？</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">第 08 课节点 1–3 的检查题：8 个专家的 MoE 层改成逐个专家调用时，后 7 次调用的并行度。</t>
+          <t xml:space="preserve">8 个专家的 MoE 层改成逐个专家调用，估计后 7 次调用的并行度时。</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -72,17 +72,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">MoE 层的输出维 N=500、输入维 K=1024，数据是 fp16。Triton 教程的描述符版 grouped GEMM 要求行步长的字节数是 16 的倍数，并且 B 按转置后的 \[N, K\] 存放：A 是 \[M, 1024\]，B 是 \[500, 1024\]，C 是 \[M, 500\]。哪个矩阵不满足要求？</t>
+          <t xml:space="preserve">Triton 3.7.1 教程的描述符版 grouped GEMM 用 TMA 读写 A、B、C，要求每个矩阵的行步长字节数都是 16 的倍数，并要求 B 按转置后的 \[N, K\] 存放。MoE 层的输出维 N=500、输入维 K=1024，数据是 fp16。A、B、C 中哪个矩阵不满足要求？</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">第 08 课节点 5 的检查题，把专家的输出维从 512 改成 500 之后。</t>
+          <t xml:space="preserve">把专家的输出维从 512 改成 500 之后，判断描述符版还能不能直接用。</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">只有 C 不满足：它每行 500 个元素，行步长 1000 字节。B 转置存放后每行 1024 个元素，行步长 2048 字节，满足要求。</t>
+          <t xml:space="preserve">只有 C 不满足：C 是 \[M, 500\]，每行 500 个元素，行步长 1000 字节。A 是 \[M, 1024\]，B 转置存放为 \[500, 1024\]，每行都是 1024 个元素、2048 字节，满足要求。</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -92,8 +92,8 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：行步长由每行有多少个元素决定，也就是矩阵的最后一维；转置存放把 B 的最后一维从 N 换成了 K。
-• [T#B#对照]：同一个 N=500：指针版里 B 是 \[1024, 500\]，坏的是 B；描述符版里 B 是 \[500, 1024\]，坏的是 C。
+          <t xml:space="preserve">[T#B,!36b59d#结论]：错在没有用上 B 转置存放这一条件：行步长由每行有多少个元素决定，也就是矩阵的最后一维；转置存放把 B 的最后一维从 N 换成了 K。
+• [T#B#对照]：同一个 N=500：指针版的 B 按 \[K, N\] 存为 \[1024, 500\]，坏的是 B（C 在指针版里没有对齐保证）；描述符版里坏的是 C。
 • [T#B#C 的修法]：分配时把行步长留宽，例如 504 个元素，再切出前 500 列，不需要拷贝。
 [T#B,!c47f17#边界]：判断时先确认是哪个版本、每个矩阵按什么形状存放，再算各自的行步长。</t>
         </is>
@@ -107,12 +107,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">第 08 课综合验收的设计题，可以使用原子操作。</t>
+          <t xml:space="preserve">允许使用原子操作。</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">显存里放一个整数计数器，含义是下一个没人领的块编号，发射前清零。每个 CTA 空闲时做一次原子的读出旧值并加 1，读到的旧值就是它领到的块；旧值超过总块数就退出。</t>
+          <t xml:space="preserve">显存里放一个整数计数器，含义是下一个没人领的块编号，发射前清零。每个 CTA 空闲时做一次原子的读出旧值并加 1，读到的旧值就是它领到的块；旧值不小于总块数就退出。</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -124,8 +124,8 @@
         <is>
           <t xml:space="preserve">[T#B,!36b59d#结论]：一个计数器就把找和抢合成了一步：读出旧值并加 1 是不可分割的，两个 CTA 读到的旧值一定不同。
 • [T#B#标记方案的代价]：每块一个标记，发射前要逐个清零，领取时要搜索哪个还空着，多个 CTA 抢同一个标记时输的还要重试。
-• [T#B#扫描仍然成立]：计数器只增不减，同一个 CTA 先后领到的编号一定递增，所以它仍然只需顺序走一遍问题表。
 • [T#B#新增的代价]：每领一块做一次原子操作，所有 CTA 争同一个地址；谁领到哪一块每次运行都不同。
+• [T#B#延伸]：计数器只增不减，同一个 CTA 先后领到的编号一定递增，所以它仍然只需顺序走一遍问题表。
 [T#B,!c47f17#边界]：一次领多块可以减少原子操作，但均衡变粗：调度模型里一次领 16 块比静态分配还差，因为成批领到的块来自同一个问题。各块工作量相同时，动态领取没有收益。</t>
         </is>
       </c>
@@ -138,7 +138,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">第 08 课综合验收的迁移题：一个没有 TMA、也没有异步拷贝的新后端，对 grouped_mm 什么都不做。</t>
+          <t xml:space="preserve">一个没有 TMA、也没有异步拷贝的新后端，对 grouped_mm 什么都不做。</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -156,19 +156,19 @@
           <t xml:space="preserve">[T#B,!36b59d#结论]：漏掉的是同步：各组的行数在设备上，而回退是在主机上逐组循环，循环之前必须把偏移表读回来。
 • [T#B#同步的含义]：读回设备上的张量时，主机要等 GPU 把排在前面的工作全部做完才能继续。
 • [T#B#快速路径的做法]：在设备上用一个小 kernel 从偏移表算出每组的地址和行数，全程不读回。
-[T#B,!c47f17#边界]：所以给新后端做适配时，让行数留在设备上应当排在搬运方式之前；否则一次发射省下的时间会被这次同步吃掉。</t>
+[T#B,!c47f17#边界]：快速路径只在 sm_90 或 sm_100、且输入输出都是 bf16 时启用，其余情况都走这条回退路径。</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">x 是 \[总行数, K\] 的 fp16 张量，各组的行在 x 里首尾相接。要在设备上建一张 int64 的地址表，第 g 项是第 g 组第一行的地址：以 x.data_ptr() 为基础，加上的偏移量应该怎样算？</t>
+          <t xml:space="preserve">用 Triton 3.7.1 写堆叠接口时，x 是 \[总行数, K\] 的 fp16 张量，各组的行在 x 里首尾相接。要在设备上建一张 int64 的地址表，第 g 项是第 g 组第一行的地址：以 x.data_ptr() 为基础，加上的偏移量应该怎样算？</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">第 08 课练习的无提示变式：堆叠接口。首版的结果里前面的行正确，中间的行被写错，最后的行从未被写入。</t>
+          <t xml:space="preserve">堆叠接口的首版：输出里前面的行正确，中间的行被写错，最后的行从未被写入。</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -194,17 +194,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">偏移表 offs 是设备上的 int32 张量，记录各组的结束行。x 有 262,144 行，每行 7168 个 fp16 元素。要在设备上算每组起始行的字节偏移，应该怎样写才不会出错？</t>
+          <t xml:space="preserve">在 PyTorch 2.13 里，堆叠接口要在设备上按偏移表算各组第一行的字节偏移。接口规定 offs 是设备上的 int32 张量，记录各组的结束行，与 PyTorch grouped_mm 的约定一致；x 有 262,144 行，每行 7168 个 fp16 元素。溢出会发生在哪一步？不改接口，应该怎样写？</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">第 08 课练习里的预测题：堆叠接口修好之后，把规模换成 DeepSeek-V3 的输入维。</t>
+          <t xml:space="preserve">把规模换成 DeepSeek-V3 的输入维 7168 时。</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">接口上的 offs 保持 int32；计算时先在设备上把它转成 int64，再乘行步长和元素大小。</t>
+          <t xml:space="preserve">溢出发生在乘法：起始行 × 行步长 × 元素大小的乘积超出了 int32。接口上的 offs 保持 int32，计算时先在设备上把它转成 int64，再乘行步长和元素大小。</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -214,9 +214,9 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：溢出的是乘积，不是 offs：行号 262,144 远小于 int32 的上限，而 261,120 × 7168 × 2 = 3,743,416,320 已经超过它。
+          <t xml:space="preserve">[T#B,!36b59d#结论]：判断溢出和列出的算式都对，错在修法：溢出的是乘积，不是 offs。行号最大 262,144，远小于 int32 的上限；而从第 261,120 行开始的一组（例如最后 1024 行那一组），字节偏移是 261,120 × 7168 × 2 = 3,743,416,320，已经超过上限。
 • [T#B#不会报错]：PyTorch 的 int32 张量乘 Python 整数，结果仍是 int32，溢出后悄悄回绕；这个例子会得到 −551,550,976。
-• [T#B#为什么不改接口]：偏移表本身不需要更宽的类型，PyTorch 的 grouped_mm 要求的也是 int32。
+• [T#B#为什么不改接口]：偏移表本身不需要更宽的类型；PyTorch 的 grouped_mm 要求的也是 int32，int64 的偏移表会被它的输入检查拒绝。
 • [T#B#PyTorch 的做法]：它在设备侧的 C++ 代码里把 offs 和 int64 的步长相乘，C++ 先把 offs 提升到 int64 再乘。
 [T#B,!c47f17#边界]：在设备上做类型转换不算把 offs 读回主机。</t>
         </is>
@@ -225,121 +225,122 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">grouped GEMM 的包装函数要为整组问题选择 kernel 的特化：只加行方向 mask 的快路径，要求每个问题的 N、K 都是块大小的整数倍；否则用三个方向都加 mask 的通用路径。应该依据什么来选？</t>
+          <t xml:space="preserve">Triton 3.7.1 的 grouped GEMM 包装函数要保证一组矩阵都在同一个设备上。这项检查保护的是 kernel 的哪个假定？因此检查时，每个张量应该和谁比较？</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">第 08 课练习的首次提交。当时的验收测试全部通过，Review 时才发现。</t>
+          <t xml:space="preserve">逐项说明包装函数的检查各保护 kernel 的哪个假定时，谈到设备检查。</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">遍历所有问题：只要有一个问题的 N 或 K 不是整块，就选通用路径。</t>
+          <t xml:space="preserve">它保护的假定是：表里的每个地址在 kernel 运行的设备上都有效。所以所有问题的 A、B 和 out 都要和同一个设备比较，例如第一个问题的 A 所在的设备。</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">在遍历完所有问题之后写 if N % block_n==0 and K % block_k == 0，用的是循环里剩下的、最后一个问题的 N 和 K</t>
+          <t xml:space="preserve">第六项设备检查，本kernel启动要求cuda。去掉可能会有编译或者计算错误</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：快路径的前提是每个问题都满足条件，所以判断必须覆盖整组；循环结束后留在变量里的只是最后一个问题的值。
-• [T#B#现象]：不整块的问题排在整块问题前面时，它被按满块处理：结果含 NaN，输出的保护区被改写。
-• [T#B#为什么测试没发现]：原有测试里凡是含不整块问题的组，最后一个问题恰好都不整块。
-[T#B,!c47f17#边界]：补上的测试把不整块的问题放在最前和中间：一个标志由整组共同决定时，测试输入要变换特殊元素的位置。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：错在把这项检查理解成“需要 CUDA”。五张表只能建在一个设备上；表里若放着另一个设备的地址，kernel 就会在 GPU 上解引用别处的内存，这是非法访问。
+• [T#B#没有人替你查]：Triton 只验证五张表本身是不是设备上的张量，表里装的地址没有任何检查。
+• [T#B#首版代码]：首版在循环里写 device = group_a\[i\].device，每个问题只和自己比较：同一问题内 A、B 设备不同能被拒绝，两个问题各自整体在不同设备上时却漏掉。
+[T#B,!c47f17#边界]：给了 CTA 数时，CPU 上的张量也可以交给 Triton 的解释器运行，所以设备检查不能写成只接受 CUDA 张量。</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">grouped GEMM 的包装函数要保证一组矩阵都在同一个设备上。检查时，每个张量应该和谁比较？这项检查保护的是 kernel 的哪个假定？</t>
+          <t xml:space="preserve">Triton 3.7.1 中，一个用了 tl.multiple_of 的 kernel，它的包装函数检查输入的 dtype、维数、行内连续性和 16 字节对齐。这几项检查里，哪一项即使被删掉，数值测试也无法稳定发现？这类检查应该怎样测？</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">第 08 课练习的第二次提交和 A6 的说明。同一个问题里 A、B 设备不同的情形能被拒绝，但两个问题各自整体在不同设备上时没有被拒绝。</t>
+          <t xml:space="preserve">逐项分析删掉某项检查后，哪些测试还能发现问题。</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">所有问题的 A、B 和 out 都和同一个设备比较，例如第一个问题的 A 所在的设备。它保护的假定是：表里的每个地址在 kernel 运行的设备上都有效。</t>
+          <t xml:space="preserve">对齐检查。违反 tl.multiple_of 的保证属未定义行为，结果可能对、可能错，也可能报异常，数值测试无法稳定发现；只能用参数测试覆盖：构造不对齐的输入，断言包装函数抛出 ValueError。</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">在循环里写 device = group_a\[i\].device，每个问题只和自己比较</t>
+          <t xml:space="preserve">选了维数检查：“如果多出来的维度全是1，可能也不会有异常，因为也相当于原本的形状。这可能会导致数值测试也无法稳定发现。”</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：五张表只能建在一个设备上；如果表里放着另一个设备的地址，kernel 就会在 GPU 上解引用别处的内存，这是非法访问。
-• [T#B#没有人替你查]：Triton 只验证五张表本身是不是设备上的张量，表里装的地址没有任何检查。
-• [T#B#怎样安全地测]：测试里用一个不发射的替身代替 kernel，缺少检查的实现也不会真的把跨设备的地址交给 GPU；只有 CPU 的机器上可以用 PyTorch 的 meta 设备充当第二个设备。
-[T#B,!c47f17#边界]：这项检查的目的不是要求 CUDA：给了 CTA 数时，CPU 上的张量也可以交给 Triton 的解释器运行。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：错在选了维数检查：去掉它，代码行为不变，\[1, 64, 64\] 这样的输入仍被后面的行内连续检查拦住、抛出 ValueError，没有被数值掩盖的隐患。
+• [T#B#对齐为什么特殊]：编译器和运行时都不检查 tl.multiple_of 的保证。保证不成立时，kernel 请求的字节和解释方式都不变，被违反的只是异步拷贝指令的前提：属未定义行为，可能触发 misaligned address 之类的异常，也可能静默读错或碰巧正确。
+• [T#B#和另外两项的区别]：dtype 和行内连续性出错时，改变的是读到哪些字节、怎样解释它们，每次运行、每台设备都错成同一个样子，随机数据必然暴露。
+• [T#B#解释器看不到]：Triton 的 CPU 解释器完全忽略这个保证，行步长 200 字节的输入算出来和 torch.matmul 一致。
+[T#B,!c47f17#边界]：未对齐的输入在真实 GPU 上会怎样没有实测；说删掉对齐检查“可能会报错”并不算错，问题在于不能指望它稳定报错。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">一个用了 tl.multiple_of 的 Triton kernel，它的包装函数检查输入的 dtype、行内连续性和 16 字节对齐。这几项检查里，哪一项即使被删掉，数值测试也无法稳定发现？这类检查应该怎样测？</t>
+          <t xml:space="preserve">Triton 3.7.1 指针版 grouped GEMM 的 kernel 里，A、B 的块指针经过 tl.multiple_of(…, \[16, 16\])，C 的块指针直接交给带 mask 的 tl.store 写回。调用方提供的输出张量首地址对齐、行内连续，但行步长是 200 字节，不是 16 的倍数。包装函数应该拒绝它吗，为什么？</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">第 08 课练习的 A6：说明包装函数的每项检查保护 kernel 的哪个假定。当时选的是维数检查，并认为删掉对齐检查会报错。</t>
+          <t xml:space="preserve">复查包装函数的每项检查是否都有对应的 kernel 假定。</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">对齐检查。它只能用参数测试覆盖：构造不对齐的输入，断言包装函数抛出 ValueError。</t>
+          <t xml:space="preserve">不应该拒绝。kernel 对 C 没有任何对齐假定：C 由逐个元素的 2 字节写指令写回，不受行步长影响。</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">如果去掉，可能会异步拷贝报错</t>
+          <t xml:space="preserve">处理正确。否则不报错进入kernel，会导致后续的tl.multiple_of前提保证不成立</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：tl.multiple_of 不被检查。保证不成立时，kernel 请求的仍是同样的字节，被违反的只是异步拷贝指令的前提：这是未定义行为，没有报错这个环节。
-• [T#B#和另外两项的区别]：dtype 和行内连续性出错时，改变的是读到哪些字节、怎样解释它们，每次运行、每台设备都错成同一个样子，随机数据必然暴露。
-• [T#B#解释器看不到]：Triton 的 CPU 解释器完全忽略这个保证，行步长 200 字节的输入算出来和 torch.matmul 一致。
-[T#B,!c47f17#边界]：未对齐的输入在真实硬件上会怎样没有实测；正因为结果可能对也可能错，才不能指望数值测试。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：错在把对齐保证算到了 C 上：保证只存在于调用了 tl.multiple_of 的那个指针上，C 的指针从没有传给它，所以没有什么前提可以被违反。
+• [T#B#编译产物]：编译出的中间表示里，记录保证的属性只出现在 A、B 上；A、B 用 16 字节的异步拷贝，C 是每次 2 字节的普通写。
+• [T#B#可能的来源]：这个误解很可能来自描述符版（推测）：那里 C 由 TMA 整块写回，才要求对齐。
+• [T#B#多余检查的代价]：它拒绝了 kernel 能正确写入的输出，调用方只能先写进另一块缓冲区再拷一次。
+[T#B,!c47f17#边界]：如果给 C 的指针也写上保证，把写回变成每次 16 字节，那时才需要检查 C 的对齐。</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">指针版 grouped GEMM 的 kernel 只对 A、B 的指针调用了 tl.multiple_of，写回 C 用带 mask 的 tl.store。调用方提供的输出张量首地址对齐、行内连续，但行步长是 200 字节，不是 16 的倍数。包装函数应该拒绝它吗？</t>
+          <t xml:space="preserve">PyTorch 2.13 的 grouped_mm 和 Triton 教程的描述符版 grouped GEMM 都对输入矩阵的内存布局有要求，不满足的输入只能先拷贝一份。这个要求具体是什么？</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">第 08 课练习 A6 的复查题。同一个误解在节点 5 的检查题和包装函数的实现里也出现过，这是第三次。</t>
+          <t xml:space="preserve">说明输入为什么不能像输出那样靠多分配来解决时。</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">不应该拒绝。kernel 对 C 没有任何对齐假定：C 由逐个元素的 2 字节写指令写回，不受行步长影响。</t>
+          <t xml:space="preserve">要求的是行步长（相邻两行的间隔）的字节数是 16 的倍数，不是整个张量连续。</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">处理正确。否则不报错进入kernel，会导致后续的tl.multiple_of前提保证不成立</t>
+          <t xml:space="preserve">但是对于grouped_mm的输入矩阵描述符版，则必须要连续化</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：保证只存在于调用了 tl.multiple_of 的那个指针上；C 的指针从没有传给它，所以没有什么前提可以被违反。
-• [T#B#编译产物]：中间表示里记录保证的属性只出现 2 次，对应 A 和 B；A、B 用 16 字节的异步拷贝，C 是 32 条每次 2 字节的写。
-• [T#B#误解的来源]：描述符版里 C 由 TMA 整块写回，那里才要求行步长是 16 字节的倍数；PyTorch 给输出补宽行步长，走的也是那条路。
-• [T#B#多余检查的代价]：它拒绝了 kernel 能正确写入的输出，调用方只能先写进另一块缓冲区再拷一次。
-[T#B,!c47f17#边界]：如果给 C 的指针也写上保证，把写回变成每次 16 字节，那时才需要检查 C 的对齐。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：错在把对齐说成了连续：对齐条件看的是相邻两行相隔多少字节，和张量是否连续无关。
+• [T#B#连续也可能不满足]：K=1020 的 fp16 输入连续存放时，每行 2040 字节，不是 16 的倍数；连续化之后仍不满足。
+• [T#B#不连续也可能满足]：grouped_mm 自己分配的 \[768, 500\] 输出，相邻两行相隔 504 个元素、每行只用 500 列，在 PyTorch 里是不连续的张量，行步长却是 1008 字节，正好满足这条对齐要求。
+[T#B,!c47f17#边界]：所以输入不满足时，要拷进一块行步长加宽到 16 字节倍数的缓冲区；.contiguous() 只在每行字节数本来就是 16 的倍数时才顺带满足要求。</t>
         </is>
       </c>
     </row>

--- a/docs/triton-learning/cards/triton-lesson-08-grouped-gemm-correction.xlsx
+++ b/docs/triton-learning/cards/triton-lesson-08-grouped-gemm-correction.xlsx
@@ -265,7 +265,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">对齐检查。违反 tl.multiple_of 的保证属未定义行为，结果可能对、可能错，也可能报异常，数值测试无法稳定发现；只能用参数测试覆盖：构造不对齐的输入，断言包装函数抛出 ValueError。</t>
+          <t xml:space="preserve">对齐检查。违反 tl.multiple_of 的保证属未定义行为，结果取决于设备，不是数值比较能稳定发现的；只能用参数测试覆盖：构造不对齐的输入，断言包装函数在发射前抛出 ValueError。</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -276,10 +276,10 @@
       <c r="E9" t="inlineStr">
         <is>
           <t xml:space="preserve">[T#B,!36b59d#结论]：错在选了维数检查：去掉它，代码行为不变，\[1, 64, 64\] 这样的输入仍被后面的行内连续检查拦住、抛出 ValueError，没有被数值掩盖的隐患。
-• [T#B#对齐为什么特殊]：编译器和运行时都不检查 tl.multiple_of 的保证。保证不成立时，kernel 请求的字节和解释方式都不变，被违反的只是异步拷贝指令的前提：属未定义行为，可能触发 misaligned address 之类的异常，也可能静默读错或碰巧正确。
+• [T#B#对齐为什么特殊]：编译器和运行时都不检查 tl.multiple_of 的保证。保证不成立时，kernel 请求的字节和解释方式都不变，被违反的只是异步拷贝指令的前提：属未定义行为。H100 上实测（Triton 3.7.1 与 3.8.0）直接报 misaligned address，而且此后整个进程的 CUDA 都不能再用，测试会话跟着中断；其他后端未实测。
 • [T#B#和另外两项的区别]：dtype 和行内连续性出错时，改变的是读到哪些字节、怎样解释它们，每次运行、每台设备都错成同一个样子，随机数据必然暴露。
 • [T#B#解释器看不到]：Triton 的 CPU 解释器完全忽略这个保证，行步长 200 字节的输入算出来和 torch.matmul 一致。
-[T#B,!c47f17#边界]：未对齐的输入在真实 GPU 上会怎样没有实测；说删掉对齐检查“可能会报错”并不算错，问题在于不能指望它稳定报错。</t>
+[T#B,!c47f17#边界]：说删掉对齐检查“可能会报错”并不算错：H100 上确实报错。问题在于结果取决于设备，CPU 解释器上照样算对，不能把报错当作检查。</t>
         </is>
       </c>
     </row>
